--- a/Zero Leprosy Project 2025 (Karachi).xlsx
+++ b/Zero Leprosy Project 2025 (Karachi).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shah\Desktop\Master Dashboards\Zero_Lap_New_DBoard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5F2000-C04B-4B02-83D3-961483D8970F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0420DA-F0E1-4F87-BE02-AE702A93511F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38C9D9F6-D026-4EF1-BEA7-585F2FE82814}"/>
   </bookViews>
@@ -901,6 +901,62 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -947,62 +1003,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -1307,83 +1307,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
     </row>
     <row r="2" spans="1:20" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
+      <c r="A2" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
     </row>
     <row r="3" spans="1:20" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
     </row>
     <row r="4" spans="1:20" s="5" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
       <c r="D4" s="4" t="s">
         <v>4</v>
       </c>
@@ -1437,10 +1437,10 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="23" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -1499,8 +1499,8 @@
       </c>
     </row>
     <row r="6" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31"/>
-      <c r="B6" s="42"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="23"/>
       <c r="C6" s="6" t="s">
         <v>24</v>
       </c>
@@ -1557,8 +1557,8 @@
       </c>
     </row>
     <row r="7" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="31"/>
-      <c r="B7" s="42"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="23"/>
       <c r="C7" s="6" t="s">
         <v>25</v>
       </c>
@@ -1615,10 +1615,10 @@
       </c>
     </row>
     <row r="8" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -1677,8 +1677,8 @@
       </c>
     </row>
     <row r="9" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="38"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="6" t="s">
         <v>24</v>
       </c>
@@ -1735,8 +1735,8 @@
       </c>
     </row>
     <row r="10" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31"/>
-      <c r="B10" s="38"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="6" t="s">
         <v>25</v>
       </c>
@@ -1793,10 +1793,10 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="19" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -1855,8 +1855,8 @@
       </c>
     </row>
     <row r="12" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="31"/>
-      <c r="B12" s="33"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="19"/>
       <c r="C12" s="6" t="s">
         <v>24</v>
       </c>
@@ -1913,8 +1913,8 @@
       </c>
     </row>
     <row r="13" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="31"/>
-      <c r="B13" s="33"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="19"/>
       <c r="C13" s="6" t="s">
         <v>25</v>
       </c>
@@ -1971,10 +1971,10 @@
       </c>
     </row>
     <row r="14" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="19" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -2033,8 +2033,8 @@
       </c>
     </row>
     <row r="15" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31"/>
-      <c r="B15" s="33"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="19"/>
       <c r="C15" s="6" t="s">
         <v>24</v>
       </c>
@@ -2091,8 +2091,8 @@
       </c>
     </row>
     <row r="16" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="31"/>
-      <c r="B16" s="33"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="19"/>
       <c r="C16" s="6" t="s">
         <v>25</v>
       </c>
@@ -2149,10 +2149,10 @@
       </c>
     </row>
     <row r="17" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="29" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="6" t="s">
@@ -2211,8 +2211,8 @@
       </c>
     </row>
     <row r="18" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="36"/>
-      <c r="B18" s="37"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
       <c r="C18" s="6" t="s">
         <v>24</v>
       </c>
@@ -2269,8 +2269,8 @@
       </c>
     </row>
     <row r="19" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="36"/>
-      <c r="B19" s="37"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="29"/>
       <c r="C19" s="6" t="s">
         <v>25</v>
       </c>
@@ -2327,10 +2327,10 @@
       </c>
     </row>
     <row r="20" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="19" t="s">
         <v>35</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -2389,8 +2389,8 @@
       </c>
     </row>
     <row r="21" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="32"/>
-      <c r="B21" s="33"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="6" t="s">
         <v>24</v>
       </c>
@@ -2447,8 +2447,8 @@
       </c>
     </row>
     <row r="22" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="32"/>
-      <c r="B22" s="33"/>
+      <c r="A22" s="24"/>
+      <c r="B22" s="19"/>
       <c r="C22" s="6" t="s">
         <v>25</v>
       </c>
@@ -2505,10 +2505,10 @@
       </c>
     </row>
     <row r="23" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="19" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="6" t="s">
@@ -2567,8 +2567,8 @@
       </c>
     </row>
     <row r="24" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="32"/>
-      <c r="B24" s="33"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="19"/>
       <c r="C24" s="6" t="s">
         <v>24</v>
       </c>
@@ -2625,8 +2625,8 @@
       </c>
     </row>
     <row r="25" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="32"/>
-      <c r="B25" s="33"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="19"/>
       <c r="C25" s="6" t="s">
         <v>25</v>
       </c>
@@ -2683,10 +2683,10 @@
       </c>
     </row>
     <row r="26" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="19" t="s">
         <v>39</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -2745,8 +2745,8 @@
       </c>
     </row>
     <row r="27" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="32"/>
-      <c r="B27" s="33"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="19"/>
       <c r="C27" s="6" t="s">
         <v>24</v>
       </c>
@@ -2803,8 +2803,8 @@
       </c>
     </row>
     <row r="28" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="32"/>
-      <c r="B28" s="33"/>
+      <c r="A28" s="24"/>
+      <c r="B28" s="19"/>
       <c r="C28" s="6" t="s">
         <v>25</v>
       </c>
@@ -2861,10 +2861,10 @@
       </c>
     </row>
     <row r="29" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="30" t="s">
+      <c r="B29" s="27" t="s">
         <v>41</v>
       </c>
       <c r="C29" s="10" t="s">
@@ -2923,8 +2923,8 @@
       </c>
     </row>
     <row r="30" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
-      <c r="B30" s="30"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="10" t="s">
         <v>24</v>
       </c>
@@ -2981,8 +2981,8 @@
       </c>
     </row>
     <row r="31" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
-      <c r="B31" s="30"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="27"/>
       <c r="C31" s="10" t="s">
         <v>25</v>
       </c>
@@ -3039,10 +3039,10 @@
       </c>
     </row>
     <row r="32" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="27" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="10" t="s">
@@ -3101,8 +3101,8 @@
       </c>
     </row>
     <row r="33" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="34"/>
-      <c r="B33" s="30"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="27"/>
       <c r="C33" s="10" t="s">
         <v>24</v>
       </c>
@@ -3159,8 +3159,8 @@
       </c>
     </row>
     <row r="34" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
-      <c r="B34" s="30"/>
+      <c r="A34" s="26"/>
+      <c r="B34" s="27"/>
       <c r="C34" s="10" t="s">
         <v>25</v>
       </c>
@@ -3217,10 +3217,10 @@
       </c>
     </row>
     <row r="35" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="33" t="s">
+      <c r="B35" s="19" t="s">
         <v>45</v>
       </c>
       <c r="C35" s="6" t="s">
@@ -3279,8 +3279,8 @@
       </c>
     </row>
     <row r="36" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="32"/>
-      <c r="B36" s="33"/>
+      <c r="A36" s="24"/>
+      <c r="B36" s="19"/>
       <c r="C36" s="6" t="s">
         <v>24</v>
       </c>
@@ -3337,8 +3337,8 @@
       </c>
     </row>
     <row r="37" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="32"/>
-      <c r="B37" s="33"/>
+      <c r="A37" s="24"/>
+      <c r="B37" s="19"/>
       <c r="C37" s="6" t="s">
         <v>25</v>
       </c>
@@ -3395,10 +3395,10 @@
       </c>
     </row>
     <row r="38" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="33" t="s">
+      <c r="B38" s="19" t="s">
         <v>47</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -3457,8 +3457,8 @@
       </c>
     </row>
     <row r="39" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="31"/>
-      <c r="B39" s="33"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="19"/>
       <c r="C39" s="6" t="s">
         <v>24</v>
       </c>
@@ -3515,8 +3515,8 @@
       </c>
     </row>
     <row r="40" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="31"/>
-      <c r="B40" s="33"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="19"/>
       <c r="C40" s="6" t="s">
         <v>25</v>
       </c>
@@ -3573,10 +3573,10 @@
       </c>
     </row>
     <row r="41" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="33" t="s">
+      <c r="B41" s="19" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -3635,8 +3635,8 @@
       </c>
     </row>
     <row r="42" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="31"/>
-      <c r="B42" s="33"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="19"/>
       <c r="C42" s="6" t="s">
         <v>24</v>
       </c>
@@ -3693,8 +3693,8 @@
       </c>
     </row>
     <row r="43" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="31"/>
-      <c r="B43" s="33"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="19"/>
       <c r="C43" s="6" t="s">
         <v>25</v>
       </c>
@@ -3751,10 +3751,10 @@
       </c>
     </row>
     <row r="44" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="35" t="s">
+      <c r="A44" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="B44" s="30" t="s">
+      <c r="B44" s="27" t="s">
         <v>51</v>
       </c>
       <c r="C44" s="10" t="s">
@@ -3813,8 +3813,8 @@
       </c>
     </row>
     <row r="45" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="35"/>
-      <c r="B45" s="30"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="27"/>
       <c r="C45" s="10" t="s">
         <v>24</v>
       </c>
@@ -3871,8 +3871,8 @@
       </c>
     </row>
     <row r="46" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="35"/>
-      <c r="B46" s="30"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="27"/>
       <c r="C46" s="10" t="s">
         <v>25</v>
       </c>
@@ -3929,10 +3929,10 @@
       </c>
     </row>
     <row r="47" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="35" t="s">
+      <c r="A47" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="30" t="s">
+      <c r="B47" s="27" t="s">
         <v>53</v>
       </c>
       <c r="C47" s="10" t="s">
@@ -3991,8 +3991,8 @@
       </c>
     </row>
     <row r="48" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="35"/>
-      <c r="B48" s="30"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="27"/>
       <c r="C48" s="10" t="s">
         <v>24</v>
       </c>
@@ -4049,8 +4049,8 @@
       </c>
     </row>
     <row r="49" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="35"/>
-      <c r="B49" s="30"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="27"/>
       <c r="C49" s="10" t="s">
         <v>25</v>
       </c>
@@ -4107,10 +4107,10 @@
       </c>
     </row>
     <row r="50" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="35" t="s">
+      <c r="A50" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="30" t="s">
+      <c r="B50" s="27" t="s">
         <v>55</v>
       </c>
       <c r="C50" s="10" t="s">
@@ -4169,8 +4169,8 @@
       </c>
     </row>
     <row r="51" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="35"/>
-      <c r="B51" s="30"/>
+      <c r="A51" s="30"/>
+      <c r="B51" s="27"/>
       <c r="C51" s="10" t="s">
         <v>24</v>
       </c>
@@ -4227,8 +4227,8 @@
       </c>
     </row>
     <row r="52" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="35"/>
-      <c r="B52" s="30"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="27"/>
       <c r="C52" s="10" t="s">
         <v>25</v>
       </c>
@@ -4285,10 +4285,10 @@
       </c>
     </row>
     <row r="53" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="31" t="s">
+      <c r="A53" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="33" t="s">
+      <c r="B53" s="19" t="s">
         <v>57</v>
       </c>
       <c r="C53" s="6" t="s">
@@ -4347,8 +4347,8 @@
       </c>
     </row>
     <row r="54" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="32"/>
-      <c r="B54" s="33"/>
+      <c r="A54" s="24"/>
+      <c r="B54" s="19"/>
       <c r="C54" s="6" t="s">
         <v>24</v>
       </c>
@@ -4405,8 +4405,8 @@
       </c>
     </row>
     <row r="55" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="32"/>
-      <c r="B55" s="33"/>
+      <c r="A55" s="24"/>
+      <c r="B55" s="19"/>
       <c r="C55" s="6" t="s">
         <v>25</v>
       </c>
@@ -4463,10 +4463,10 @@
       </c>
     </row>
     <row r="56" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="33" t="s">
+      <c r="B56" s="19" t="s">
         <v>59</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -4525,8 +4525,8 @@
       </c>
     </row>
     <row r="57" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="32"/>
-      <c r="B57" s="33"/>
+      <c r="A57" s="24"/>
+      <c r="B57" s="19"/>
       <c r="C57" s="6" t="s">
         <v>24</v>
       </c>
@@ -4583,8 +4583,8 @@
       </c>
     </row>
     <row r="58" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="32"/>
-      <c r="B58" s="33"/>
+      <c r="A58" s="24"/>
+      <c r="B58" s="19"/>
       <c r="C58" s="6" t="s">
         <v>25</v>
       </c>
@@ -4641,10 +4641,10 @@
       </c>
     </row>
     <row r="59" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="31" t="s">
+      <c r="A59" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B59" s="33" t="s">
+      <c r="B59" s="19" t="s">
         <v>61</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -4703,8 +4703,8 @@
       </c>
     </row>
     <row r="60" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="32"/>
-      <c r="B60" s="33"/>
+      <c r="A60" s="24"/>
+      <c r="B60" s="19"/>
       <c r="C60" s="6" t="s">
         <v>24</v>
       </c>
@@ -4761,8 +4761,8 @@
       </c>
     </row>
     <row r="61" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="32"/>
-      <c r="B61" s="33"/>
+      <c r="A61" s="24"/>
+      <c r="B61" s="19"/>
       <c r="C61" s="6" t="s">
         <v>25</v>
       </c>
@@ -4819,10 +4819,10 @@
       </c>
     </row>
     <row r="62" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="29" t="s">
+      <c r="A62" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="30" t="s">
+      <c r="B62" s="27" t="s">
         <v>63</v>
       </c>
       <c r="C62" s="10" t="s">
@@ -4881,8 +4881,8 @@
       </c>
     </row>
     <row r="63" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="34"/>
-      <c r="B63" s="30"/>
+      <c r="A63" s="26"/>
+      <c r="B63" s="27"/>
       <c r="C63" s="10" t="s">
         <v>24</v>
       </c>
@@ -4939,8 +4939,8 @@
       </c>
     </row>
     <row r="64" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="34"/>
-      <c r="B64" s="30"/>
+      <c r="A64" s="26"/>
+      <c r="B64" s="27"/>
       <c r="C64" s="10" t="s">
         <v>25</v>
       </c>
@@ -4997,10 +4997,10 @@
       </c>
     </row>
     <row r="65" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="29" t="s">
+      <c r="A65" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="30" t="s">
+      <c r="B65" s="27" t="s">
         <v>65</v>
       </c>
       <c r="C65" s="10" t="s">
@@ -5059,8 +5059,8 @@
       </c>
     </row>
     <row r="66" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="34"/>
-      <c r="B66" s="30"/>
+      <c r="A66" s="26"/>
+      <c r="B66" s="27"/>
       <c r="C66" s="10" t="s">
         <v>24</v>
       </c>
@@ -5117,8 +5117,8 @@
       </c>
     </row>
     <row r="67" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="34"/>
-      <c r="B67" s="30"/>
+      <c r="A67" s="26"/>
+      <c r="B67" s="27"/>
       <c r="C67" s="10" t="s">
         <v>25</v>
       </c>
@@ -5175,10 +5175,10 @@
       </c>
     </row>
     <row r="68" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="29" t="s">
+      <c r="A68" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="30" t="s">
+      <c r="B68" s="27" t="s">
         <v>67</v>
       </c>
       <c r="C68" s="10" t="s">
@@ -5237,8 +5237,8 @@
       </c>
     </row>
     <row r="69" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="34"/>
-      <c r="B69" s="30"/>
+      <c r="A69" s="26"/>
+      <c r="B69" s="27"/>
       <c r="C69" s="10" t="s">
         <v>24</v>
       </c>
@@ -5295,8 +5295,8 @@
       </c>
     </row>
     <row r="70" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="34"/>
-      <c r="B70" s="30"/>
+      <c r="A70" s="26"/>
+      <c r="B70" s="27"/>
       <c r="C70" s="10" t="s">
         <v>25</v>
       </c>
@@ -5353,10 +5353,10 @@
       </c>
     </row>
     <row r="71" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="31" t="s">
+      <c r="A71" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B71" s="33" t="s">
+      <c r="B71" s="19" t="s">
         <v>69</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -5415,8 +5415,8 @@
       </c>
     </row>
     <row r="72" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="32"/>
-      <c r="B72" s="33"/>
+      <c r="A72" s="24"/>
+      <c r="B72" s="19"/>
       <c r="C72" s="6" t="s">
         <v>24</v>
       </c>
@@ -5473,8 +5473,8 @@
       </c>
     </row>
     <row r="73" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="32"/>
-      <c r="B73" s="33"/>
+      <c r="A73" s="24"/>
+      <c r="B73" s="19"/>
       <c r="C73" s="6" t="s">
         <v>25</v>
       </c>
@@ -5531,10 +5531,10 @@
       </c>
     </row>
     <row r="74" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="31" t="s">
+      <c r="A74" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B74" s="33" t="s">
+      <c r="B74" s="19" t="s">
         <v>71</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -5593,8 +5593,8 @@
       </c>
     </row>
     <row r="75" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="32"/>
-      <c r="B75" s="33"/>
+      <c r="A75" s="24"/>
+      <c r="B75" s="19"/>
       <c r="C75" s="6" t="s">
         <v>24</v>
       </c>
@@ -5651,8 +5651,8 @@
       </c>
     </row>
     <row r="76" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="32"/>
-      <c r="B76" s="33"/>
+      <c r="A76" s="24"/>
+      <c r="B76" s="19"/>
       <c r="C76" s="6" t="s">
         <v>25</v>
       </c>
@@ -5709,10 +5709,10 @@
       </c>
     </row>
     <row r="77" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="31" t="s">
+      <c r="A77" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="33" t="s">
+      <c r="B77" s="19" t="s">
         <v>73</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -5771,8 +5771,8 @@
       </c>
     </row>
     <row r="78" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="32"/>
-      <c r="B78" s="33"/>
+      <c r="A78" s="24"/>
+      <c r="B78" s="19"/>
       <c r="C78" s="6" t="s">
         <v>24</v>
       </c>
@@ -5829,8 +5829,8 @@
       </c>
     </row>
     <row r="79" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="32"/>
-      <c r="B79" s="33"/>
+      <c r="A79" s="24"/>
+      <c r="B79" s="19"/>
       <c r="C79" s="6" t="s">
         <v>25</v>
       </c>
@@ -5887,10 +5887,10 @@
       </c>
     </row>
     <row r="80" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="31" t="s">
+      <c r="A80" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B80" s="33" t="s">
+      <c r="B80" s="19" t="s">
         <v>75</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -5949,8 +5949,8 @@
       </c>
     </row>
     <row r="81" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="32"/>
-      <c r="B81" s="33"/>
+      <c r="A81" s="24"/>
+      <c r="B81" s="19"/>
       <c r="C81" s="6" t="s">
         <v>24</v>
       </c>
@@ -6007,8 +6007,8 @@
       </c>
     </row>
     <row r="82" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="32"/>
-      <c r="B82" s="33"/>
+      <c r="A82" s="24"/>
+      <c r="B82" s="19"/>
       <c r="C82" s="6" t="s">
         <v>25</v>
       </c>
@@ -6065,10 +6065,10 @@
       </c>
     </row>
     <row r="83" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="32" t="s">
+      <c r="A83" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="B83" s="33" t="s">
+      <c r="B83" s="19" t="s">
         <v>77</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -6127,8 +6127,8 @@
       </c>
     </row>
     <row r="84" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="32"/>
-      <c r="B84" s="33"/>
+      <c r="A84" s="24"/>
+      <c r="B84" s="19"/>
       <c r="C84" s="6" t="s">
         <v>24</v>
       </c>
@@ -6185,8 +6185,8 @@
       </c>
     </row>
     <row r="85" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="32"/>
-      <c r="B85" s="33"/>
+      <c r="A85" s="24"/>
+      <c r="B85" s="19"/>
       <c r="C85" s="6" t="s">
         <v>25</v>
       </c>
@@ -6243,10 +6243,10 @@
       </c>
     </row>
     <row r="86" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="31" t="s">
+      <c r="A86" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B86" s="33" t="s">
+      <c r="B86" s="19" t="s">
         <v>79</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -6305,8 +6305,8 @@
       </c>
     </row>
     <row r="87" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="32"/>
-      <c r="B87" s="33"/>
+      <c r="A87" s="24"/>
+      <c r="B87" s="19"/>
       <c r="C87" s="6" t="s">
         <v>24</v>
       </c>
@@ -6363,8 +6363,8 @@
       </c>
     </row>
     <row r="88" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="32"/>
-      <c r="B88" s="33"/>
+      <c r="A88" s="24"/>
+      <c r="B88" s="19"/>
       <c r="C88" s="6" t="s">
         <v>25</v>
       </c>
@@ -6421,10 +6421,10 @@
       </c>
     </row>
     <row r="89" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="29" t="s">
+      <c r="A89" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="B89" s="30" t="s">
+      <c r="B89" s="27" t="s">
         <v>81</v>
       </c>
       <c r="C89" s="10" t="s">
@@ -6483,8 +6483,8 @@
       </c>
     </row>
     <row r="90" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="34"/>
-      <c r="B90" s="30"/>
+      <c r="A90" s="26"/>
+      <c r="B90" s="27"/>
       <c r="C90" s="10" t="s">
         <v>24</v>
       </c>
@@ -6541,8 +6541,8 @@
       </c>
     </row>
     <row r="91" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="34"/>
-      <c r="B91" s="30"/>
+      <c r="A91" s="26"/>
+      <c r="B91" s="27"/>
       <c r="C91" s="10" t="s">
         <v>25</v>
       </c>
@@ -6599,10 +6599,10 @@
       </c>
     </row>
     <row r="92" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="29" t="s">
+      <c r="A92" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="B92" s="30" t="s">
+      <c r="B92" s="27" t="s">
         <v>83</v>
       </c>
       <c r="C92" s="10" t="s">
@@ -6661,8 +6661,8 @@
       </c>
     </row>
     <row r="93" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="34"/>
-      <c r="B93" s="30"/>
+      <c r="A93" s="26"/>
+      <c r="B93" s="27"/>
       <c r="C93" s="10" t="s">
         <v>24</v>
       </c>
@@ -6719,8 +6719,8 @@
       </c>
     </row>
     <row r="94" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="34"/>
-      <c r="B94" s="30"/>
+      <c r="A94" s="26"/>
+      <c r="B94" s="27"/>
       <c r="C94" s="10" t="s">
         <v>25</v>
       </c>
@@ -6777,10 +6777,10 @@
       </c>
     </row>
     <row r="95" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="31" t="s">
+      <c r="A95" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="B95" s="33" t="s">
+      <c r="B95" s="19" t="s">
         <v>85</v>
       </c>
       <c r="C95" s="6" t="s">
@@ -6839,8 +6839,8 @@
       </c>
     </row>
     <row r="96" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="32"/>
-      <c r="B96" s="33"/>
+      <c r="A96" s="24"/>
+      <c r="B96" s="19"/>
       <c r="C96" s="6" t="s">
         <v>24</v>
       </c>
@@ -6897,8 +6897,8 @@
       </c>
     </row>
     <row r="97" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="32"/>
-      <c r="B97" s="33"/>
+      <c r="A97" s="24"/>
+      <c r="B97" s="19"/>
       <c r="C97" s="6" t="s">
         <v>25</v>
       </c>
@@ -6955,10 +6955,10 @@
       </c>
     </row>
     <row r="98" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="31" t="s">
+      <c r="A98" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B98" s="33" t="s">
+      <c r="B98" s="19" t="s">
         <v>87</v>
       </c>
       <c r="C98" s="6" t="s">
@@ -7017,8 +7017,8 @@
       </c>
     </row>
     <row r="99" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="32"/>
-      <c r="B99" s="33"/>
+      <c r="A99" s="24"/>
+      <c r="B99" s="19"/>
       <c r="C99" s="6" t="s">
         <v>24</v>
       </c>
@@ -7075,8 +7075,8 @@
       </c>
     </row>
     <row r="100" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="32"/>
-      <c r="B100" s="33"/>
+      <c r="A100" s="24"/>
+      <c r="B100" s="19"/>
       <c r="C100" s="6" t="s">
         <v>25</v>
       </c>
@@ -7133,10 +7133,10 @@
       </c>
     </row>
     <row r="101" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="31" t="s">
+      <c r="A101" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B101" s="33" t="s">
+      <c r="B101" s="19" t="s">
         <v>89</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -7195,8 +7195,8 @@
       </c>
     </row>
     <row r="102" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="32"/>
-      <c r="B102" s="33"/>
+      <c r="A102" s="24"/>
+      <c r="B102" s="19"/>
       <c r="C102" s="6" t="s">
         <v>24</v>
       </c>
@@ -7253,8 +7253,8 @@
       </c>
     </row>
     <row r="103" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="32"/>
-      <c r="B103" s="33"/>
+      <c r="A103" s="24"/>
+      <c r="B103" s="19"/>
       <c r="C103" s="6" t="s">
         <v>25</v>
       </c>
@@ -7311,10 +7311,10 @@
       </c>
     </row>
     <row r="104" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="31" t="s">
+      <c r="A104" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B104" s="33" t="s">
+      <c r="B104" s="19" t="s">
         <v>91</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -7373,8 +7373,8 @@
       </c>
     </row>
     <row r="105" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="32"/>
-      <c r="B105" s="33"/>
+      <c r="A105" s="24"/>
+      <c r="B105" s="19"/>
       <c r="C105" s="6" t="s">
         <v>24</v>
       </c>
@@ -7431,8 +7431,8 @@
       </c>
     </row>
     <row r="106" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="32"/>
-      <c r="B106" s="33"/>
+      <c r="A106" s="24"/>
+      <c r="B106" s="19"/>
       <c r="C106" s="6" t="s">
         <v>25</v>
       </c>
@@ -7489,10 +7489,10 @@
       </c>
     </row>
     <row r="107" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="29" t="s">
+      <c r="A107" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="B107" s="30" t="s">
+      <c r="B107" s="27" t="s">
         <v>93</v>
       </c>
       <c r="C107" s="10" t="s">
@@ -7551,8 +7551,8 @@
       </c>
     </row>
     <row r="108" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="29"/>
-      <c r="B108" s="30"/>
+      <c r="A108" s="25"/>
+      <c r="B108" s="27"/>
       <c r="C108" s="10" t="s">
         <v>24</v>
       </c>
@@ -7609,8 +7609,8 @@
       </c>
     </row>
     <row r="109" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="29"/>
-      <c r="B109" s="30"/>
+      <c r="A109" s="25"/>
+      <c r="B109" s="27"/>
       <c r="C109" s="10" t="s">
         <v>25</v>
       </c>
@@ -7667,10 +7667,10 @@
       </c>
     </row>
     <row r="110" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="17" t="s">
+      <c r="A110" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="B110" s="20" t="s">
+      <c r="B110" s="34" t="s">
         <v>95</v>
       </c>
       <c r="C110" s="10" t="s">
@@ -7729,8 +7729,8 @@
       </c>
     </row>
     <row r="111" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="18"/>
-      <c r="B111" s="21"/>
+      <c r="A111" s="32"/>
+      <c r="B111" s="35"/>
       <c r="C111" s="10" t="s">
         <v>24</v>
       </c>
@@ -7787,8 +7787,8 @@
       </c>
     </row>
     <row r="112" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="19"/>
-      <c r="B112" s="22"/>
+      <c r="A112" s="33"/>
+      <c r="B112" s="36"/>
       <c r="C112" s="10" t="s">
         <v>25</v>
       </c>
@@ -7845,10 +7845,10 @@
       </c>
     </row>
     <row r="113" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="17" t="s">
+      <c r="A113" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="B113" s="20" t="s">
+      <c r="B113" s="34" t="s">
         <v>97</v>
       </c>
       <c r="C113" s="10" t="s">
@@ -7907,8 +7907,8 @@
       </c>
     </row>
     <row r="114" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="18"/>
-      <c r="B114" s="21"/>
+      <c r="A114" s="32"/>
+      <c r="B114" s="35"/>
       <c r="C114" s="10" t="s">
         <v>24</v>
       </c>
@@ -7965,8 +7965,8 @@
       </c>
     </row>
     <row r="115" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="19"/>
-      <c r="B115" s="22"/>
+      <c r="A115" s="33"/>
+      <c r="B115" s="36"/>
       <c r="C115" s="10" t="s">
         <v>25</v>
       </c>
@@ -8023,10 +8023,10 @@
       </c>
     </row>
     <row r="116" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="17" t="s">
+      <c r="A116" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="B116" s="20" t="s">
+      <c r="B116" s="34" t="s">
         <v>99</v>
       </c>
       <c r="C116" s="10" t="s">
@@ -8085,8 +8085,8 @@
       </c>
     </row>
     <row r="117" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="18"/>
-      <c r="B117" s="21"/>
+      <c r="A117" s="32"/>
+      <c r="B117" s="35"/>
       <c r="C117" s="10" t="s">
         <v>24</v>
       </c>
@@ -8143,8 +8143,8 @@
       </c>
     </row>
     <row r="118" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="19"/>
-      <c r="B118" s="22"/>
+      <c r="A118" s="33"/>
+      <c r="B118" s="36"/>
       <c r="C118" s="10" t="s">
         <v>25</v>
       </c>
@@ -8201,10 +8201,10 @@
       </c>
     </row>
     <row r="119" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="23" t="s">
+      <c r="A119" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="B119" s="26" t="s">
+      <c r="B119" s="40" t="s">
         <v>101</v>
       </c>
       <c r="C119" s="6" t="s">
@@ -8263,8 +8263,8 @@
       </c>
     </row>
     <row r="120" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="24"/>
-      <c r="B120" s="27"/>
+      <c r="A120" s="38"/>
+      <c r="B120" s="41"/>
       <c r="C120" s="6" t="s">
         <v>24</v>
       </c>
@@ -8321,8 +8321,8 @@
       </c>
     </row>
     <row r="121" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="25"/>
-      <c r="B121" s="28"/>
+      <c r="A121" s="39"/>
+      <c r="B121" s="42"/>
       <c r="C121" s="6" t="s">
         <v>25</v>
       </c>
@@ -8379,10 +8379,10 @@
       </c>
     </row>
     <row r="122" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="23" t="s">
+      <c r="A122" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="B122" s="26" t="s">
+      <c r="B122" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C122" s="6" t="s">
@@ -8441,8 +8441,8 @@
       </c>
     </row>
     <row r="123" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="24"/>
-      <c r="B123" s="27"/>
+      <c r="A123" s="38"/>
+      <c r="B123" s="41"/>
       <c r="C123" s="6" t="s">
         <v>24</v>
       </c>
@@ -8499,8 +8499,8 @@
       </c>
     </row>
     <row r="124" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="25"/>
-      <c r="B124" s="28"/>
+      <c r="A124" s="39"/>
+      <c r="B124" s="42"/>
       <c r="C124" s="6" t="s">
         <v>25</v>
       </c>
@@ -8557,10 +8557,10 @@
       </c>
     </row>
     <row r="125" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="17" t="s">
+      <c r="A125" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="B125" s="20" t="s">
+      <c r="B125" s="34" t="s">
         <v>105</v>
       </c>
       <c r="C125" s="10" t="s">
@@ -8619,8 +8619,8 @@
       </c>
     </row>
     <row r="126" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="18"/>
-      <c r="B126" s="21"/>
+      <c r="A126" s="32"/>
+      <c r="B126" s="35"/>
       <c r="C126" s="10" t="s">
         <v>24</v>
       </c>
@@ -8677,8 +8677,8 @@
       </c>
     </row>
     <row r="127" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="19"/>
-      <c r="B127" s="22"/>
+      <c r="A127" s="33"/>
+      <c r="B127" s="36"/>
       <c r="C127" s="10" t="s">
         <v>25</v>
       </c>
@@ -8735,10 +8735,10 @@
       </c>
     </row>
     <row r="128" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="17" t="s">
+      <c r="A128" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="B128" s="20" t="s">
+      <c r="B128" s="34" t="s">
         <v>107</v>
       </c>
       <c r="C128" s="10" t="s">
@@ -8797,8 +8797,8 @@
       </c>
     </row>
     <row r="129" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="18"/>
-      <c r="B129" s="21"/>
+      <c r="A129" s="32"/>
+      <c r="B129" s="35"/>
       <c r="C129" s="10" t="s">
         <v>24</v>
       </c>
@@ -8855,8 +8855,8 @@
       </c>
     </row>
     <row r="130" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="19"/>
-      <c r="B130" s="22"/>
+      <c r="A130" s="33"/>
+      <c r="B130" s="36"/>
       <c r="C130" s="10" t="s">
         <v>25</v>
       </c>
@@ -8913,10 +8913,10 @@
       </c>
     </row>
     <row r="131" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="17" t="s">
+      <c r="A131" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="B131" s="20" t="s">
+      <c r="B131" s="34" t="s">
         <v>109</v>
       </c>
       <c r="C131" s="10" t="s">
@@ -8975,8 +8975,8 @@
       </c>
     </row>
     <row r="132" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="18"/>
-      <c r="B132" s="21"/>
+      <c r="A132" s="32"/>
+      <c r="B132" s="35"/>
       <c r="C132" s="10" t="s">
         <v>24</v>
       </c>
@@ -9033,8 +9033,8 @@
       </c>
     </row>
     <row r="133" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="19"/>
-      <c r="B133" s="22"/>
+      <c r="A133" s="33"/>
+      <c r="B133" s="36"/>
       <c r="C133" s="10" t="s">
         <v>25</v>
       </c>
@@ -9091,10 +9091,10 @@
       </c>
     </row>
     <row r="134" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="23" t="s">
+      <c r="A134" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="B134" s="26" t="s">
+      <c r="B134" s="40" t="s">
         <v>111</v>
       </c>
       <c r="C134" s="6" t="s">
@@ -9153,8 +9153,8 @@
       </c>
     </row>
     <row r="135" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="24"/>
-      <c r="B135" s="27"/>
+      <c r="A135" s="38"/>
+      <c r="B135" s="41"/>
       <c r="C135" s="6" t="s">
         <v>24</v>
       </c>
@@ -9211,8 +9211,8 @@
       </c>
     </row>
     <row r="136" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="25"/>
-      <c r="B136" s="28"/>
+      <c r="A136" s="39"/>
+      <c r="B136" s="42"/>
       <c r="C136" s="6" t="s">
         <v>25</v>
       </c>
@@ -9269,10 +9269,10 @@
       </c>
     </row>
     <row r="137" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="23" t="s">
+      <c r="A137" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="B137" s="26" t="s">
+      <c r="B137" s="40" t="s">
         <v>113</v>
       </c>
       <c r="C137" s="6" t="s">
@@ -9331,8 +9331,8 @@
       </c>
     </row>
     <row r="138" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="24"/>
-      <c r="B138" s="27"/>
+      <c r="A138" s="38"/>
+      <c r="B138" s="41"/>
       <c r="C138" s="6" t="s">
         <v>24</v>
       </c>
@@ -9389,8 +9389,8 @@
       </c>
     </row>
     <row r="139" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="25"/>
-      <c r="B139" s="28"/>
+      <c r="A139" s="39"/>
+      <c r="B139" s="42"/>
       <c r="C139" s="6" t="s">
         <v>25</v>
       </c>
@@ -9447,10 +9447,10 @@
       </c>
     </row>
     <row r="140" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="17" t="s">
+      <c r="A140" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="B140" s="20" t="s">
+      <c r="B140" s="34" t="s">
         <v>115</v>
       </c>
       <c r="C140" s="10" t="s">
@@ -9509,8 +9509,8 @@
       </c>
     </row>
     <row r="141" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="18"/>
-      <c r="B141" s="21"/>
+      <c r="A141" s="32"/>
+      <c r="B141" s="35"/>
       <c r="C141" s="10" t="s">
         <v>24</v>
       </c>
@@ -9567,8 +9567,8 @@
       </c>
     </row>
     <row r="142" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="19"/>
-      <c r="B142" s="22"/>
+      <c r="A142" s="33"/>
+      <c r="B142" s="36"/>
       <c r="C142" s="10" t="s">
         <v>25</v>
       </c>
@@ -9625,10 +9625,10 @@
       </c>
     </row>
     <row r="143" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="17" t="s">
+      <c r="A143" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="B143" s="20" t="s">
+      <c r="B143" s="34" t="s">
         <v>117</v>
       </c>
       <c r="C143" s="10" t="s">
@@ -9687,8 +9687,8 @@
       </c>
     </row>
     <row r="144" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="18"/>
-      <c r="B144" s="21"/>
+      <c r="A144" s="32"/>
+      <c r="B144" s="35"/>
       <c r="C144" s="10" t="s">
         <v>24</v>
       </c>
@@ -9745,8 +9745,8 @@
       </c>
     </row>
     <row r="145" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="19"/>
-      <c r="B145" s="22"/>
+      <c r="A145" s="33"/>
+      <c r="B145" s="36"/>
       <c r="C145" s="10" t="s">
         <v>25</v>
       </c>
@@ -9803,10 +9803,10 @@
       </c>
     </row>
     <row r="146" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="23" t="s">
+      <c r="A146" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="B146" s="26" t="s">
+      <c r="B146" s="40" t="s">
         <v>119</v>
       </c>
       <c r="C146" s="6" t="s">
@@ -9865,8 +9865,8 @@
       </c>
     </row>
     <row r="147" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="24"/>
-      <c r="B147" s="27"/>
+      <c r="A147" s="38"/>
+      <c r="B147" s="41"/>
       <c r="C147" s="6" t="s">
         <v>24</v>
       </c>
@@ -9923,8 +9923,8 @@
       </c>
     </row>
     <row r="148" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="25"/>
-      <c r="B148" s="28"/>
+      <c r="A148" s="39"/>
+      <c r="B148" s="42"/>
       <c r="C148" s="6" t="s">
         <v>25</v>
       </c>
@@ -9981,10 +9981,10 @@
       </c>
     </row>
     <row r="149" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="17" t="s">
+      <c r="A149" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="B149" s="20" t="s">
+      <c r="B149" s="34" t="s">
         <v>121</v>
       </c>
       <c r="C149" s="10" t="s">
@@ -10043,8 +10043,8 @@
       </c>
     </row>
     <row r="150" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="18"/>
-      <c r="B150" s="21"/>
+      <c r="A150" s="32"/>
+      <c r="B150" s="35"/>
       <c r="C150" s="10" t="s">
         <v>24</v>
       </c>
@@ -10101,8 +10101,8 @@
       </c>
     </row>
     <row r="151" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="19"/>
-      <c r="B151" s="22"/>
+      <c r="A151" s="33"/>
+      <c r="B151" s="36"/>
       <c r="C151" s="10" t="s">
         <v>25</v>
       </c>
@@ -10159,10 +10159,10 @@
       </c>
     </row>
     <row r="152" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="17" t="s">
+      <c r="A152" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="B152" s="20" t="s">
+      <c r="B152" s="34" t="s">
         <v>123</v>
       </c>
       <c r="C152" s="10" t="s">
@@ -10221,8 +10221,8 @@
       </c>
     </row>
     <row r="153" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="18"/>
-      <c r="B153" s="21"/>
+      <c r="A153" s="32"/>
+      <c r="B153" s="35"/>
       <c r="C153" s="10" t="s">
         <v>24</v>
       </c>
@@ -10279,8 +10279,8 @@
       </c>
     </row>
     <row r="154" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="19"/>
-      <c r="B154" s="22"/>
+      <c r="A154" s="33"/>
+      <c r="B154" s="36"/>
       <c r="C154" s="10" t="s">
         <v>25</v>
       </c>
@@ -10337,10 +10337,10 @@
       </c>
     </row>
     <row r="155" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="23" t="s">
+      <c r="A155" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="B155" s="26" t="s">
+      <c r="B155" s="40" t="s">
         <v>125</v>
       </c>
       <c r="C155" s="6" t="s">
@@ -10399,8 +10399,8 @@
       </c>
     </row>
     <row r="156" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="24"/>
-      <c r="B156" s="27"/>
+      <c r="A156" s="38"/>
+      <c r="B156" s="41"/>
       <c r="C156" s="6" t="s">
         <v>24</v>
       </c>
@@ -10457,8 +10457,8 @@
       </c>
     </row>
     <row r="157" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="25"/>
-      <c r="B157" s="28"/>
+      <c r="A157" s="39"/>
+      <c r="B157" s="42"/>
       <c r="C157" s="6" t="s">
         <v>25</v>
       </c>
@@ -10515,10 +10515,10 @@
       </c>
     </row>
     <row r="158" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="23" t="s">
+      <c r="A158" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="B158" s="26" t="s">
+      <c r="B158" s="40" t="s">
         <v>127</v>
       </c>
       <c r="C158" s="6" t="s">
@@ -10577,8 +10577,8 @@
       </c>
     </row>
     <row r="159" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="24"/>
-      <c r="B159" s="27"/>
+      <c r="A159" s="38"/>
+      <c r="B159" s="41"/>
       <c r="C159" s="6" t="s">
         <v>24</v>
       </c>
@@ -10635,8 +10635,8 @@
       </c>
     </row>
     <row r="160" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="25"/>
-      <c r="B160" s="28"/>
+      <c r="A160" s="39"/>
+      <c r="B160" s="42"/>
       <c r="C160" s="6" t="s">
         <v>25</v>
       </c>
@@ -10693,10 +10693,10 @@
       </c>
     </row>
     <row r="161" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="17" t="s">
+      <c r="A161" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="B161" s="20" t="s">
+      <c r="B161" s="34" t="s">
         <v>129</v>
       </c>
       <c r="C161" s="10" t="s">
@@ -10755,8 +10755,8 @@
       </c>
     </row>
     <row r="162" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="18"/>
-      <c r="B162" s="21"/>
+      <c r="A162" s="32"/>
+      <c r="B162" s="35"/>
       <c r="C162" s="10" t="s">
         <v>24</v>
       </c>
@@ -10813,8 +10813,8 @@
       </c>
     </row>
     <row r="163" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="19"/>
-      <c r="B163" s="22"/>
+      <c r="A163" s="33"/>
+      <c r="B163" s="36"/>
       <c r="C163" s="10" t="s">
         <v>25</v>
       </c>
@@ -10871,10 +10871,10 @@
       </c>
     </row>
     <row r="164" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="17" t="s">
+      <c r="A164" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="B164" s="20" t="s">
+      <c r="B164" s="34" t="s">
         <v>131</v>
       </c>
       <c r="C164" s="10" t="s">
@@ -10933,8 +10933,8 @@
       </c>
     </row>
     <row r="165" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="18"/>
-      <c r="B165" s="21"/>
+      <c r="A165" s="32"/>
+      <c r="B165" s="35"/>
       <c r="C165" s="10" t="s">
         <v>24</v>
       </c>
@@ -10991,8 +10991,8 @@
       </c>
     </row>
     <row r="166" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="19"/>
-      <c r="B166" s="22"/>
+      <c r="A166" s="33"/>
+      <c r="B166" s="36"/>
       <c r="C166" s="10" t="s">
         <v>25</v>
       </c>
@@ -11049,10 +11049,10 @@
       </c>
     </row>
     <row r="167" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="17" t="s">
+      <c r="A167" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="B167" s="20" t="s">
+      <c r="B167" s="34" t="s">
         <v>133</v>
       </c>
       <c r="C167" s="10" t="s">
@@ -11111,8 +11111,8 @@
       </c>
     </row>
     <row r="168" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="18"/>
-      <c r="B168" s="21"/>
+      <c r="A168" s="32"/>
+      <c r="B168" s="35"/>
       <c r="C168" s="10" t="s">
         <v>24</v>
       </c>
@@ -11169,8 +11169,8 @@
       </c>
     </row>
     <row r="169" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="19"/>
-      <c r="B169" s="22"/>
+      <c r="A169" s="33"/>
+      <c r="B169" s="36"/>
       <c r="C169" s="10" t="s">
         <v>25</v>
       </c>
@@ -11227,10 +11227,10 @@
       </c>
     </row>
     <row r="170" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="17" t="s">
+      <c r="A170" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="B170" s="20" t="s">
+      <c r="B170" s="34" t="s">
         <v>135</v>
       </c>
       <c r="C170" s="10" t="s">
@@ -11289,8 +11289,8 @@
       </c>
     </row>
     <row r="171" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="18"/>
-      <c r="B171" s="21"/>
+      <c r="A171" s="32"/>
+      <c r="B171" s="35"/>
       <c r="C171" s="10" t="s">
         <v>24</v>
       </c>
@@ -11347,8 +11347,8 @@
       </c>
     </row>
     <row r="172" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="19"/>
-      <c r="B172" s="22"/>
+      <c r="A172" s="33"/>
+      <c r="B172" s="36"/>
       <c r="C172" s="10" t="s">
         <v>25</v>
       </c>
@@ -11405,10 +11405,10 @@
       </c>
     </row>
     <row r="173" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="17" t="s">
+      <c r="A173" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="B173" s="20" t="s">
+      <c r="B173" s="34" t="s">
         <v>137</v>
       </c>
       <c r="C173" s="10" t="s">
@@ -11467,8 +11467,8 @@
       </c>
     </row>
     <row r="174" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="18"/>
-      <c r="B174" s="21"/>
+      <c r="A174" s="32"/>
+      <c r="B174" s="35"/>
       <c r="C174" s="10" t="s">
         <v>24</v>
       </c>
@@ -11525,8 +11525,8 @@
       </c>
     </row>
     <row r="175" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="19"/>
-      <c r="B175" s="22"/>
+      <c r="A175" s="33"/>
+      <c r="B175" s="36"/>
       <c r="C175" s="10" t="s">
         <v>25</v>
       </c>
@@ -11583,10 +11583,10 @@
       </c>
     </row>
     <row r="176" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="17" t="s">
+      <c r="A176" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="B176" s="20" t="s">
+      <c r="B176" s="34" t="s">
         <v>139</v>
       </c>
       <c r="C176" s="10" t="s">
@@ -11645,8 +11645,8 @@
       </c>
     </row>
     <row r="177" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="18"/>
-      <c r="B177" s="21"/>
+      <c r="A177" s="32"/>
+      <c r="B177" s="35"/>
       <c r="C177" s="10" t="s">
         <v>24</v>
       </c>
@@ -11703,8 +11703,8 @@
       </c>
     </row>
     <row r="178" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="19"/>
-      <c r="B178" s="22"/>
+      <c r="A178" s="33"/>
+      <c r="B178" s="36"/>
       <c r="C178" s="10" t="s">
         <v>25</v>
       </c>
@@ -11761,10 +11761,10 @@
       </c>
     </row>
     <row r="179" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="17" t="s">
+      <c r="A179" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="B179" s="20" t="s">
+      <c r="B179" s="34" t="s">
         <v>141</v>
       </c>
       <c r="C179" s="10" t="s">
@@ -11823,8 +11823,8 @@
       </c>
     </row>
     <row r="180" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="18"/>
-      <c r="B180" s="21"/>
+      <c r="A180" s="32"/>
+      <c r="B180" s="35"/>
       <c r="C180" s="10" t="s">
         <v>24</v>
       </c>
@@ -11881,8 +11881,8 @@
       </c>
     </row>
     <row r="181" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="19"/>
-      <c r="B181" s="22"/>
+      <c r="A181" s="33"/>
+      <c r="B181" s="36"/>
       <c r="C181" s="10" t="s">
         <v>25</v>
       </c>
@@ -11939,10 +11939,10 @@
       </c>
     </row>
     <row r="182" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="17" t="s">
+      <c r="A182" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="B182" s="20" t="s">
+      <c r="B182" s="34" t="s">
         <v>143</v>
       </c>
       <c r="C182" s="14" t="s">
@@ -12001,8 +12001,8 @@
       </c>
     </row>
     <row r="183" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="18"/>
-      <c r="B183" s="21"/>
+      <c r="A183" s="32"/>
+      <c r="B183" s="35"/>
       <c r="C183" s="14" t="s">
         <v>24</v>
       </c>
@@ -12059,8 +12059,8 @@
       </c>
     </row>
     <row r="184" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="19"/>
-      <c r="B184" s="22"/>
+      <c r="A184" s="33"/>
+      <c r="B184" s="36"/>
       <c r="C184" s="14" t="s">
         <v>25</v>
       </c>
@@ -12117,10 +12117,10 @@
       </c>
     </row>
     <row r="185" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="17" t="s">
+      <c r="A185" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="B185" s="20" t="s">
+      <c r="B185" s="34" t="s">
         <v>145</v>
       </c>
       <c r="C185" s="14" t="s">
@@ -12179,8 +12179,8 @@
       </c>
     </row>
     <row r="186" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="18"/>
-      <c r="B186" s="21"/>
+      <c r="A186" s="32"/>
+      <c r="B186" s="35"/>
       <c r="C186" s="14" t="s">
         <v>24</v>
       </c>
@@ -12237,8 +12237,8 @@
       </c>
     </row>
     <row r="187" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="19"/>
-      <c r="B187" s="22"/>
+      <c r="A187" s="33"/>
+      <c r="B187" s="36"/>
       <c r="C187" s="14" t="s">
         <v>25</v>
       </c>
@@ -12295,10 +12295,10 @@
       </c>
     </row>
     <row r="188" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="17" t="s">
+      <c r="A188" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="B188" s="20" t="s">
+      <c r="B188" s="34" t="s">
         <v>147</v>
       </c>
       <c r="C188" s="14" t="s">
@@ -12357,8 +12357,8 @@
       </c>
     </row>
     <row r="189" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="18"/>
-      <c r="B189" s="21"/>
+      <c r="A189" s="32"/>
+      <c r="B189" s="35"/>
       <c r="C189" s="14" t="s">
         <v>24</v>
       </c>
@@ -12415,8 +12415,8 @@
       </c>
     </row>
     <row r="190" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="19"/>
-      <c r="B190" s="22"/>
+      <c r="A190" s="33"/>
+      <c r="B190" s="36"/>
       <c r="C190" s="14" t="s">
         <v>25</v>
       </c>
@@ -12473,10 +12473,10 @@
       </c>
     </row>
     <row r="191" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="17" t="s">
+      <c r="A191" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="B191" s="20" t="s">
+      <c r="B191" s="34" t="s">
         <v>149</v>
       </c>
       <c r="C191" s="10" t="s">
@@ -12535,8 +12535,8 @@
       </c>
     </row>
     <row r="192" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="18"/>
-      <c r="B192" s="21"/>
+      <c r="A192" s="32"/>
+      <c r="B192" s="35"/>
       <c r="C192" s="10" t="s">
         <v>24</v>
       </c>
@@ -12593,8 +12593,8 @@
       </c>
     </row>
     <row r="193" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="19"/>
-      <c r="B193" s="22"/>
+      <c r="A193" s="33"/>
+      <c r="B193" s="36"/>
       <c r="C193" s="10" t="s">
         <v>25</v>
       </c>
@@ -12651,10 +12651,10 @@
       </c>
     </row>
     <row r="194" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="17" t="s">
+      <c r="A194" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="B194" s="20" t="s">
+      <c r="B194" s="34" t="s">
         <v>151</v>
       </c>
       <c r="C194" s="10" t="s">
@@ -12713,8 +12713,8 @@
       </c>
     </row>
     <row r="195" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="18"/>
-      <c r="B195" s="21"/>
+      <c r="A195" s="32"/>
+      <c r="B195" s="35"/>
       <c r="C195" s="10" t="s">
         <v>24</v>
       </c>
@@ -12771,8 +12771,8 @@
       </c>
     </row>
     <row r="196" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="19"/>
-      <c r="B196" s="22"/>
+      <c r="A196" s="33"/>
+      <c r="B196" s="36"/>
       <c r="C196" s="10" t="s">
         <v>25</v>
       </c>
@@ -12829,10 +12829,10 @@
       </c>
     </row>
     <row r="197" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="23" t="s">
+      <c r="A197" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="B197" s="26" t="s">
+      <c r="B197" s="40" t="s">
         <v>153</v>
       </c>
       <c r="C197" s="6" t="s">
@@ -12891,8 +12891,8 @@
       </c>
     </row>
     <row r="198" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="24"/>
-      <c r="B198" s="27"/>
+      <c r="A198" s="38"/>
+      <c r="B198" s="41"/>
       <c r="C198" s="6" t="s">
         <v>24</v>
       </c>
@@ -12949,8 +12949,8 @@
       </c>
     </row>
     <row r="199" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="25"/>
-      <c r="B199" s="28"/>
+      <c r="A199" s="39"/>
+      <c r="B199" s="42"/>
       <c r="C199" s="6" t="s">
         <v>25</v>
       </c>
@@ -13007,10 +13007,10 @@
       </c>
     </row>
     <row r="200" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="23" t="s">
+      <c r="A200" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="B200" s="26" t="s">
+      <c r="B200" s="40" t="s">
         <v>155</v>
       </c>
       <c r="C200" s="6" t="s">
@@ -13069,8 +13069,8 @@
       </c>
     </row>
     <row r="201" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="24"/>
-      <c r="B201" s="27"/>
+      <c r="A201" s="38"/>
+      <c r="B201" s="41"/>
       <c r="C201" s="6" t="s">
         <v>24</v>
       </c>
@@ -13127,8 +13127,8 @@
       </c>
     </row>
     <row r="202" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="25"/>
-      <c r="B202" s="28"/>
+      <c r="A202" s="39"/>
+      <c r="B202" s="42"/>
       <c r="C202" s="6" t="s">
         <v>25</v>
       </c>
@@ -13185,10 +13185,10 @@
       </c>
     </row>
     <row r="203" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="23" t="s">
+      <c r="A203" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="B203" s="26" t="s">
+      <c r="B203" s="40" t="s">
         <v>157</v>
       </c>
       <c r="C203" s="6" t="s">
@@ -13247,8 +13247,8 @@
       </c>
     </row>
     <row r="204" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="24"/>
-      <c r="B204" s="27"/>
+      <c r="A204" s="38"/>
+      <c r="B204" s="41"/>
       <c r="C204" s="6" t="s">
         <v>24</v>
       </c>
@@ -13305,8 +13305,8 @@
       </c>
     </row>
     <row r="205" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="25"/>
-      <c r="B205" s="28"/>
+      <c r="A205" s="39"/>
+      <c r="B205" s="42"/>
       <c r="C205" s="6" t="s">
         <v>25</v>
       </c>
@@ -13363,10 +13363,10 @@
       </c>
     </row>
     <row r="206" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="23" t="s">
+      <c r="A206" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="B206" s="26" t="s">
+      <c r="B206" s="40" t="s">
         <v>159</v>
       </c>
       <c r="C206" s="6" t="s">
@@ -13425,8 +13425,8 @@
       </c>
     </row>
     <row r="207" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="24"/>
-      <c r="B207" s="27"/>
+      <c r="A207" s="38"/>
+      <c r="B207" s="41"/>
       <c r="C207" s="6" t="s">
         <v>24</v>
       </c>
@@ -13483,8 +13483,8 @@
       </c>
     </row>
     <row r="208" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="25"/>
-      <c r="B208" s="28"/>
+      <c r="A208" s="39"/>
+      <c r="B208" s="42"/>
       <c r="C208" s="6" t="s">
         <v>25</v>
       </c>
@@ -13541,10 +13541,10 @@
       </c>
     </row>
     <row r="209" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="23" t="s">
+      <c r="A209" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="B209" s="26" t="s">
+      <c r="B209" s="40" t="s">
         <v>161</v>
       </c>
       <c r="C209" s="6" t="s">
@@ -13603,8 +13603,8 @@
       </c>
     </row>
     <row r="210" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="24"/>
-      <c r="B210" s="27"/>
+      <c r="A210" s="38"/>
+      <c r="B210" s="41"/>
       <c r="C210" s="6" t="s">
         <v>24</v>
       </c>
@@ -13661,8 +13661,8 @@
       </c>
     </row>
     <row r="211" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="25"/>
-      <c r="B211" s="28"/>
+      <c r="A211" s="39"/>
+      <c r="B211" s="42"/>
       <c r="C211" s="6" t="s">
         <v>25</v>
       </c>
@@ -13719,10 +13719,10 @@
       </c>
     </row>
     <row r="212" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="23" t="s">
+      <c r="A212" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="B212" s="26" t="s">
+      <c r="B212" s="40" t="s">
         <v>163</v>
       </c>
       <c r="C212" s="6" t="s">
@@ -13781,8 +13781,8 @@
       </c>
     </row>
     <row r="213" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="24"/>
-      <c r="B213" s="27"/>
+      <c r="A213" s="38"/>
+      <c r="B213" s="41"/>
       <c r="C213" s="6" t="s">
         <v>24</v>
       </c>
@@ -13839,8 +13839,8 @@
       </c>
     </row>
     <row r="214" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="25"/>
-      <c r="B214" s="28"/>
+      <c r="A214" s="39"/>
+      <c r="B214" s="42"/>
       <c r="C214" s="6" t="s">
         <v>25</v>
       </c>
@@ -13897,10 +13897,10 @@
       </c>
     </row>
     <row r="215" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="23" t="s">
+      <c r="A215" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="B215" s="26" t="s">
+      <c r="B215" s="40" t="s">
         <v>165</v>
       </c>
       <c r="C215" s="6" t="s">
@@ -13959,8 +13959,8 @@
       </c>
     </row>
     <row r="216" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="24"/>
-      <c r="B216" s="27"/>
+      <c r="A216" s="38"/>
+      <c r="B216" s="41"/>
       <c r="C216" s="6" t="s">
         <v>24</v>
       </c>
@@ -14017,8 +14017,8 @@
       </c>
     </row>
     <row r="217" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="25"/>
-      <c r="B217" s="28"/>
+      <c r="A217" s="39"/>
+      <c r="B217" s="42"/>
       <c r="C217" s="6" t="s">
         <v>25</v>
       </c>
@@ -14075,10 +14075,10 @@
       </c>
     </row>
     <row r="218" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="23" t="s">
+      <c r="A218" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="B218" s="26" t="s">
+      <c r="B218" s="40" t="s">
         <v>167</v>
       </c>
       <c r="C218" s="6" t="s">
@@ -14137,8 +14137,8 @@
       </c>
     </row>
     <row r="219" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="24"/>
-      <c r="B219" s="27"/>
+      <c r="A219" s="38"/>
+      <c r="B219" s="41"/>
       <c r="C219" s="6" t="s">
         <v>24</v>
       </c>
@@ -14195,8 +14195,8 @@
       </c>
     </row>
     <row r="220" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="25"/>
-      <c r="B220" s="28"/>
+      <c r="A220" s="39"/>
+      <c r="B220" s="42"/>
       <c r="C220" s="6" t="s">
         <v>25</v>
       </c>
@@ -14253,10 +14253,10 @@
       </c>
     </row>
     <row r="221" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="17" t="s">
+      <c r="A221" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="B221" s="20" t="s">
+      <c r="B221" s="34" t="s">
         <v>169</v>
       </c>
       <c r="C221" s="10" t="s">
@@ -14315,8 +14315,8 @@
       </c>
     </row>
     <row r="222" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="18"/>
-      <c r="B222" s="21"/>
+      <c r="A222" s="32"/>
+      <c r="B222" s="35"/>
       <c r="C222" s="10" t="s">
         <v>24</v>
       </c>
@@ -14373,8 +14373,8 @@
       </c>
     </row>
     <row r="223" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="19"/>
-      <c r="B223" s="22"/>
+      <c r="A223" s="33"/>
+      <c r="B223" s="36"/>
       <c r="C223" s="10" t="s">
         <v>25</v>
       </c>
@@ -14431,10 +14431,10 @@
       </c>
     </row>
     <row r="224" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="17" t="s">
+      <c r="A224" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="B224" s="20" t="s">
+      <c r="B224" s="34" t="s">
         <v>171</v>
       </c>
       <c r="C224" s="10" t="s">
@@ -14493,8 +14493,8 @@
       </c>
     </row>
     <row r="225" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="18"/>
-      <c r="B225" s="21"/>
+      <c r="A225" s="32"/>
+      <c r="B225" s="35"/>
       <c r="C225" s="10" t="s">
         <v>24</v>
       </c>
@@ -14551,8 +14551,8 @@
       </c>
     </row>
     <row r="226" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="19"/>
-      <c r="B226" s="22"/>
+      <c r="A226" s="33"/>
+      <c r="B226" s="36"/>
       <c r="C226" s="10" t="s">
         <v>25</v>
       </c>
@@ -14609,10 +14609,10 @@
       </c>
     </row>
     <row r="227" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="17" t="s">
+      <c r="A227" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="B227" s="20" t="s">
+      <c r="B227" s="34" t="s">
         <v>173</v>
       </c>
       <c r="C227" s="10" t="s">
@@ -14671,8 +14671,8 @@
       </c>
     </row>
     <row r="228" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="18"/>
-      <c r="B228" s="21"/>
+      <c r="A228" s="32"/>
+      <c r="B228" s="35"/>
       <c r="C228" s="10" t="s">
         <v>24</v>
       </c>
@@ -14729,8 +14729,8 @@
       </c>
     </row>
     <row r="229" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="19"/>
-      <c r="B229" s="22"/>
+      <c r="A229" s="33"/>
+      <c r="B229" s="36"/>
       <c r="C229" s="10" t="s">
         <v>25</v>
       </c>
@@ -14787,10 +14787,10 @@
       </c>
     </row>
     <row r="230" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="17" t="s">
+      <c r="A230" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="B230" s="20" t="s">
+      <c r="B230" s="34" t="s">
         <v>175</v>
       </c>
       <c r="C230" s="10" t="s">
@@ -14849,8 +14849,8 @@
       </c>
     </row>
     <row r="231" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="18"/>
-      <c r="B231" s="21"/>
+      <c r="A231" s="32"/>
+      <c r="B231" s="35"/>
       <c r="C231" s="10" t="s">
         <v>24</v>
       </c>
@@ -14907,8 +14907,8 @@
       </c>
     </row>
     <row r="232" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="19"/>
-      <c r="B232" s="22"/>
+      <c r="A232" s="33"/>
+      <c r="B232" s="36"/>
       <c r="C232" s="10" t="s">
         <v>25</v>
       </c>
@@ -14965,10 +14965,10 @@
       </c>
     </row>
     <row r="233" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="17" t="s">
+      <c r="A233" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="B233" s="20" t="s">
+      <c r="B233" s="34" t="s">
         <v>177</v>
       </c>
       <c r="C233" s="10" t="s">
@@ -15027,8 +15027,8 @@
       </c>
     </row>
     <row r="234" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="18"/>
-      <c r="B234" s="21"/>
+      <c r="A234" s="32"/>
+      <c r="B234" s="35"/>
       <c r="C234" s="10" t="s">
         <v>24</v>
       </c>
@@ -15085,8 +15085,8 @@
       </c>
     </row>
     <row r="235" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="19"/>
-      <c r="B235" s="22"/>
+      <c r="A235" s="33"/>
+      <c r="B235" s="36"/>
       <c r="C235" s="10" t="s">
         <v>25</v>
       </c>
@@ -15143,10 +15143,10 @@
       </c>
     </row>
     <row r="236" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="17" t="s">
+      <c r="A236" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="B236" s="20" t="s">
+      <c r="B236" s="34" t="s">
         <v>179</v>
       </c>
       <c r="C236" s="10" t="s">
@@ -15205,8 +15205,8 @@
       </c>
     </row>
     <row r="237" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="18"/>
-      <c r="B237" s="21"/>
+      <c r="A237" s="32"/>
+      <c r="B237" s="35"/>
       <c r="C237" s="10" t="s">
         <v>24</v>
       </c>
@@ -15263,8 +15263,8 @@
       </c>
     </row>
     <row r="238" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="19"/>
-      <c r="B238" s="22"/>
+      <c r="A238" s="33"/>
+      <c r="B238" s="36"/>
       <c r="C238" s="10" t="s">
         <v>25</v>
       </c>
@@ -15321,10 +15321,10 @@
       </c>
     </row>
     <row r="239" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="17" t="s">
+      <c r="A239" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="B239" s="20" t="s">
+      <c r="B239" s="34" t="s">
         <v>181</v>
       </c>
       <c r="C239" s="10" t="s">
@@ -15383,8 +15383,8 @@
       </c>
     </row>
     <row r="240" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="18"/>
-      <c r="B240" s="21"/>
+      <c r="A240" s="32"/>
+      <c r="B240" s="35"/>
       <c r="C240" s="10" t="s">
         <v>24</v>
       </c>
@@ -15441,8 +15441,8 @@
       </c>
     </row>
     <row r="241" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="19"/>
-      <c r="B241" s="22"/>
+      <c r="A241" s="33"/>
+      <c r="B241" s="36"/>
       <c r="C241" s="10" t="s">
         <v>25</v>
       </c>
@@ -15499,10 +15499,10 @@
       </c>
     </row>
     <row r="242" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="17" t="s">
+      <c r="A242" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B242" s="20" t="s">
+      <c r="B242" s="34" t="s">
         <v>183</v>
       </c>
       <c r="C242" s="10" t="s">
@@ -15561,8 +15561,8 @@
       </c>
     </row>
     <row r="243" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="18"/>
-      <c r="B243" s="21"/>
+      <c r="A243" s="32"/>
+      <c r="B243" s="35"/>
       <c r="C243" s="10" t="s">
         <v>24</v>
       </c>
@@ -15619,8 +15619,8 @@
       </c>
     </row>
     <row r="244" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="19"/>
-      <c r="B244" s="22"/>
+      <c r="A244" s="33"/>
+      <c r="B244" s="36"/>
       <c r="C244" s="10" t="s">
         <v>25</v>
       </c>
@@ -15677,10 +15677,10 @@
       </c>
     </row>
     <row r="245" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="17" t="s">
+      <c r="A245" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="B245" s="20" t="s">
+      <c r="B245" s="34" t="s">
         <v>185</v>
       </c>
       <c r="C245" s="10" t="s">
@@ -15739,8 +15739,8 @@
       </c>
     </row>
     <row r="246" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="18"/>
-      <c r="B246" s="21"/>
+      <c r="A246" s="32"/>
+      <c r="B246" s="35"/>
       <c r="C246" s="10" t="s">
         <v>24</v>
       </c>
@@ -15797,8 +15797,8 @@
       </c>
     </row>
     <row r="247" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="19"/>
-      <c r="B247" s="22"/>
+      <c r="A247" s="33"/>
+      <c r="B247" s="36"/>
       <c r="C247" s="10" t="s">
         <v>25</v>
       </c>
@@ -15855,10 +15855,10 @@
       </c>
     </row>
     <row r="248" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="17" t="s">
+      <c r="A248" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="B248" s="20" t="s">
+      <c r="B248" s="34" t="s">
         <v>187</v>
       </c>
       <c r="C248" s="10" t="s">
@@ -15917,8 +15917,8 @@
       </c>
     </row>
     <row r="249" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="18"/>
-      <c r="B249" s="21"/>
+      <c r="A249" s="32"/>
+      <c r="B249" s="35"/>
       <c r="C249" s="10" t="s">
         <v>24</v>
       </c>
@@ -15975,8 +15975,8 @@
       </c>
     </row>
     <row r="250" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="19"/>
-      <c r="B250" s="22"/>
+      <c r="A250" s="33"/>
+      <c r="B250" s="36"/>
       <c r="C250" s="10" t="s">
         <v>25</v>
       </c>
@@ -16033,10 +16033,10 @@
       </c>
     </row>
     <row r="251" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="17" t="s">
+      <c r="A251" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="B251" s="20" t="s">
+      <c r="B251" s="34" t="s">
         <v>189</v>
       </c>
       <c r="C251" s="10" t="s">
@@ -16095,8 +16095,8 @@
       </c>
     </row>
     <row r="252" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="18"/>
-      <c r="B252" s="21"/>
+      <c r="A252" s="32"/>
+      <c r="B252" s="35"/>
       <c r="C252" s="10" t="s">
         <v>24</v>
       </c>
@@ -16153,8 +16153,8 @@
       </c>
     </row>
     <row r="253" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A253" s="19"/>
-      <c r="B253" s="22"/>
+      <c r="A253" s="33"/>
+      <c r="B253" s="36"/>
       <c r="C253" s="10" t="s">
         <v>25</v>
       </c>
@@ -16211,10 +16211,10 @@
       </c>
     </row>
     <row r="254" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="17" t="s">
+      <c r="A254" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="B254" s="20" t="s">
+      <c r="B254" s="34" t="s">
         <v>191</v>
       </c>
       <c r="C254" s="10" t="s">
@@ -16273,8 +16273,8 @@
       </c>
     </row>
     <row r="255" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A255" s="18"/>
-      <c r="B255" s="21"/>
+      <c r="A255" s="32"/>
+      <c r="B255" s="35"/>
       <c r="C255" s="10" t="s">
         <v>24</v>
       </c>
@@ -16331,8 +16331,8 @@
       </c>
     </row>
     <row r="256" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A256" s="19"/>
-      <c r="B256" s="22"/>
+      <c r="A256" s="33"/>
+      <c r="B256" s="36"/>
       <c r="C256" s="10" t="s">
         <v>25</v>
       </c>
@@ -16389,10 +16389,10 @@
       </c>
     </row>
     <row r="257" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A257" s="17" t="s">
+      <c r="A257" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="B257" s="20" t="s">
+      <c r="B257" s="34" t="s">
         <v>193</v>
       </c>
       <c r="C257" s="10" t="s">
@@ -16451,8 +16451,8 @@
       </c>
     </row>
     <row r="258" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A258" s="18"/>
-      <c r="B258" s="21"/>
+      <c r="A258" s="32"/>
+      <c r="B258" s="35"/>
       <c r="C258" s="10" t="s">
         <v>24</v>
       </c>
@@ -16509,8 +16509,8 @@
       </c>
     </row>
     <row r="259" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="19"/>
-      <c r="B259" s="22"/>
+      <c r="A259" s="33"/>
+      <c r="B259" s="36"/>
       <c r="C259" s="10" t="s">
         <v>25</v>
       </c>
@@ -16567,10 +16567,10 @@
       </c>
     </row>
     <row r="260" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A260" s="17" t="s">
+      <c r="A260" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="B260" s="20" t="s">
+      <c r="B260" s="34" t="s">
         <v>195</v>
       </c>
       <c r="C260" s="10" t="s">
@@ -16629,8 +16629,8 @@
       </c>
     </row>
     <row r="261" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A261" s="18"/>
-      <c r="B261" s="21"/>
+      <c r="A261" s="32"/>
+      <c r="B261" s="35"/>
       <c r="C261" s="10" t="s">
         <v>24</v>
       </c>
@@ -16687,8 +16687,8 @@
       </c>
     </row>
     <row r="262" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A262" s="19"/>
-      <c r="B262" s="22"/>
+      <c r="A262" s="33"/>
+      <c r="B262" s="36"/>
       <c r="C262" s="10" t="s">
         <v>25</v>
       </c>
@@ -16745,10 +16745,10 @@
       </c>
     </row>
     <row r="263" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A263" s="17" t="s">
+      <c r="A263" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="B263" s="20" t="s">
+      <c r="B263" s="34" t="s">
         <v>197</v>
       </c>
       <c r="C263" s="10" t="s">
@@ -16807,8 +16807,8 @@
       </c>
     </row>
     <row r="264" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A264" s="18"/>
-      <c r="B264" s="21"/>
+      <c r="A264" s="32"/>
+      <c r="B264" s="35"/>
       <c r="C264" s="10" t="s">
         <v>24</v>
       </c>
@@ -16865,8 +16865,8 @@
       </c>
     </row>
     <row r="265" spans="1:20" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A265" s="19"/>
-      <c r="B265" s="22"/>
+      <c r="A265" s="33"/>
+      <c r="B265" s="36"/>
       <c r="C265" s="10" t="s">
         <v>25</v>
       </c>
@@ -16924,6 +16924,172 @@
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="A260:A262"/>
+    <mergeCell ref="B260:B262"/>
+    <mergeCell ref="A263:A265"/>
+    <mergeCell ref="B263:B265"/>
+    <mergeCell ref="A251:A253"/>
+    <mergeCell ref="B251:B253"/>
+    <mergeCell ref="A254:A256"/>
+    <mergeCell ref="B254:B256"/>
+    <mergeCell ref="A257:A259"/>
+    <mergeCell ref="B257:B259"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="B242:B244"/>
+    <mergeCell ref="A245:A247"/>
+    <mergeCell ref="B245:B247"/>
+    <mergeCell ref="A248:A250"/>
+    <mergeCell ref="B248:B250"/>
+    <mergeCell ref="A233:A235"/>
+    <mergeCell ref="B233:B235"/>
+    <mergeCell ref="A236:A238"/>
+    <mergeCell ref="B236:B238"/>
+    <mergeCell ref="A239:A241"/>
+    <mergeCell ref="B239:B241"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="B224:B226"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="B227:B229"/>
+    <mergeCell ref="A230:A232"/>
+    <mergeCell ref="B230:B232"/>
+    <mergeCell ref="A215:A217"/>
+    <mergeCell ref="B215:B217"/>
+    <mergeCell ref="A218:A220"/>
+    <mergeCell ref="B218:B220"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="B221:B223"/>
+    <mergeCell ref="A206:A208"/>
+    <mergeCell ref="B206:B208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="B209:B211"/>
+    <mergeCell ref="A212:A214"/>
+    <mergeCell ref="B212:B214"/>
+    <mergeCell ref="A197:A199"/>
+    <mergeCell ref="B197:B199"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="B200:B202"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="B203:B205"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="B188:B190"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="B191:B193"/>
+    <mergeCell ref="A194:A196"/>
+    <mergeCell ref="B194:B196"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="B179:B181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="B182:B184"/>
+    <mergeCell ref="A185:A187"/>
+    <mergeCell ref="B185:B187"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="B170:B172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="B173:B175"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="B176:B178"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="B161:B163"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="B164:B166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="B167:B169"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="B152:B154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="B155:B157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="B158:B160"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="B143:B145"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="B146:B148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="B149:B151"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="B140:B142"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="B119:B121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="B122:B124"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="B110:B112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="B104:B106"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="B80:B82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="B83:B85"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="B86:B88"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="B65:B67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B23:B25"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="A11:A13"/>
@@ -16936,172 +17102,6 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="B5:B7"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="B68:B70"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="B59:B61"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="B80:B82"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="B83:B85"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="B86:B88"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="B71:B73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="B74:B76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="B104:B106"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="B119:B121"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="B122:B124"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="B110:B112"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="B140:B142"/>
-    <mergeCell ref="A125:A127"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="A152:A154"/>
-    <mergeCell ref="B152:B154"/>
-    <mergeCell ref="A155:A157"/>
-    <mergeCell ref="B155:B157"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="B158:B160"/>
-    <mergeCell ref="A143:A145"/>
-    <mergeCell ref="B143:B145"/>
-    <mergeCell ref="A146:A148"/>
-    <mergeCell ref="B146:B148"/>
-    <mergeCell ref="A149:A151"/>
-    <mergeCell ref="B149:B151"/>
-    <mergeCell ref="A170:A172"/>
-    <mergeCell ref="B170:B172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="B173:B175"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="B176:B178"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="B161:B163"/>
-    <mergeCell ref="A164:A166"/>
-    <mergeCell ref="B164:B166"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="B167:B169"/>
-    <mergeCell ref="A188:A190"/>
-    <mergeCell ref="B188:B190"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="B191:B193"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="B194:B196"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="B179:B181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="B182:B184"/>
-    <mergeCell ref="A185:A187"/>
-    <mergeCell ref="B185:B187"/>
-    <mergeCell ref="A206:A208"/>
-    <mergeCell ref="B206:B208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="B209:B211"/>
-    <mergeCell ref="A212:A214"/>
-    <mergeCell ref="B212:B214"/>
-    <mergeCell ref="A197:A199"/>
-    <mergeCell ref="B197:B199"/>
-    <mergeCell ref="A200:A202"/>
-    <mergeCell ref="B200:B202"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="B203:B205"/>
-    <mergeCell ref="A224:A226"/>
-    <mergeCell ref="B224:B226"/>
-    <mergeCell ref="A227:A229"/>
-    <mergeCell ref="B227:B229"/>
-    <mergeCell ref="A230:A232"/>
-    <mergeCell ref="B230:B232"/>
-    <mergeCell ref="A215:A217"/>
-    <mergeCell ref="B215:B217"/>
-    <mergeCell ref="A218:A220"/>
-    <mergeCell ref="B218:B220"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="B221:B223"/>
-    <mergeCell ref="A242:A244"/>
-    <mergeCell ref="B242:B244"/>
-    <mergeCell ref="A245:A247"/>
-    <mergeCell ref="B245:B247"/>
-    <mergeCell ref="A248:A250"/>
-    <mergeCell ref="B248:B250"/>
-    <mergeCell ref="A233:A235"/>
-    <mergeCell ref="B233:B235"/>
-    <mergeCell ref="A236:A238"/>
-    <mergeCell ref="B236:B238"/>
-    <mergeCell ref="A239:A241"/>
-    <mergeCell ref="B239:B241"/>
-    <mergeCell ref="A260:A262"/>
-    <mergeCell ref="B260:B262"/>
-    <mergeCell ref="A263:A265"/>
-    <mergeCell ref="B263:B265"/>
-    <mergeCell ref="A251:A253"/>
-    <mergeCell ref="B251:B253"/>
-    <mergeCell ref="A254:A256"/>
-    <mergeCell ref="B254:B256"/>
-    <mergeCell ref="A257:A259"/>
-    <mergeCell ref="B257:B259"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="0.25" bottom="0.25" header="0.25" footer="0.25"/>
